--- a/data/trans_bre/IP1001-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,78</t>
+          <t>-1,25; 3,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 6,19</t>
+          <t>-0,51; 5,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,84</t>
+          <t>-2,53; 3,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,62</t>
+          <t>-2,1; 3,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,45; 1020,83</t>
+          <t>-37,96; 883,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-86,55; 558,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,12</t>
+          <t>-2,84; 2,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,96</t>
+          <t>-3,87; 0,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,82</t>
+          <t>-1,88; 3,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,6</t>
+          <t>-5,48; 0,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,65; 159,3</t>
+          <t>-69,87; 146,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,85; 85,07</t>
+          <t>-87,91; 72,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,79; 202,36</t>
+          <t>-46,22; 187,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,09; 36,13</t>
+          <t>-84,66; 50,3</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 6,17</t>
+          <t>-0,27; 6,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,29</t>
+          <t>-2,31; 1,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,84</t>
+          <t>-4,03; 0,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 1,01</t>
+          <t>-8,34; 1,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 732,56</t>
+          <t>-20,51; 782,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-93,8; 67,87</t>
+          <t>-91,85; 83,15</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 2,4</t>
+          <t>-4,14; 2,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,94; -0,09</t>
+          <t>-5,57; -0,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,74</t>
+          <t>-4,06; 0,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,49</t>
+          <t>-3,74; 1,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,78; 103,19</t>
+          <t>-68,63; 77,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,29; 19,88</t>
+          <t>-92,25; 21,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,25; 74,29</t>
+          <t>-89,23; 86,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,67; 187,52</t>
+          <t>-86,18; 217,56</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,71</t>
+          <t>-1,02; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,57</t>
+          <t>-2,1; 0,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,03</t>
+          <t>-1,68; 0,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,15</t>
+          <t>-3,25; 0,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,0; 81,16</t>
+          <t>-30,4; 91,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 30,22</t>
+          <t>-62,11; 28,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,94; 51,19</t>
+          <t>-50,03; 50,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-66,49; 12,66</t>
+          <t>-68,88; 15,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,24</t>
+          <t>-1,2; 3,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,9</t>
+          <t>-0,6; 6,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,54</t>
+          <t>-2,73; 3,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 3,7</t>
+          <t>-2,11; 3,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,96; 883,56</t>
+          <t>-44,2; 995,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 465,61</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,16</t>
+          <t>-2,81; 2,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,77</t>
+          <t>-3,74; 1,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,61</t>
+          <t>-1,61; 3,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,98</t>
+          <t>-5,13; 0,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 146,66</t>
+          <t>-67,17; 142,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,91; 72,33</t>
+          <t>-84,86; 105,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 187,94</t>
+          <t>-41,16; 228,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,66; 50,3</t>
+          <t>-84,24; 45,75</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 6,26</t>
+          <t>-0,28; 5,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,48</t>
+          <t>-2,3; 1,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,54</t>
+          <t>-3,63; 0,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 1,28</t>
+          <t>-8,45; 1,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,51; 782,62</t>
+          <t>-22,46; 650,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 613,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 181,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-91,85; 83,15</t>
+          <t>-90,61; 101,52</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 2,04</t>
+          <t>-4,43; 1,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,57; -0,01</t>
+          <t>-5,94; -0,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,85</t>
+          <t>-3,89; 0,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,81</t>
+          <t>-4,04; 1,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,63; 77,12</t>
+          <t>-71,28; 84,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,25; 21,58</t>
+          <t>-92,94; 9,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,23; 86,19</t>
+          <t>-89,12; 91,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,18; 217,56</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,82</t>
+          <t>-1,05; 1,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,48</t>
+          <t>-2,0; 0,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,93</t>
+          <t>-1,66; 1,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,28</t>
+          <t>-3,23; 0,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 91,15</t>
+          <t>-33,83; 88,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-62,11; 28,04</t>
+          <t>-59,97; 39,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,03; 50,12</t>
+          <t>-50,5; 63,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-68,88; 15,22</t>
+          <t>-69,98; 8,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,36</t>
+          <t>-1,14; 3,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 6,62</t>
+          <t>-0,77; 6,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,6</t>
+          <t>-2,55; 3,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 3,66</t>
+          <t>-2,16; 3,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,2; 995,04</t>
+          <t>-48,45; 1020,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 465,61</t>
+          <t>-86,55; 558,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,12</t>
+          <t>-1,92</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-46,8%</t>
+          <t>-42,35%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,11</t>
+          <t>-2,9; 2,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,03</t>
+          <t>-3,58; 0,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,83</t>
+          <t>-1,81; 3,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 0,98</t>
+          <t>-5,13; 1,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,17; 142,49</t>
+          <t>-67,65; 159,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,86; 105,42</t>
+          <t>-85,85; 85,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 228,33</t>
+          <t>-44,79; 202,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,24; 45,75</t>
+          <t>-81,34; 44,59</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,28</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-50,11%</t>
+          <t>-17,62%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 5,84</t>
+          <t>-0,09; 6,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,39</t>
+          <t>-2,56; 1,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,85</t>
+          <t>-3,63; 0,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 1,31</t>
+          <t>-4,66; 2,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 650,47</t>
+          <t>-21,72; 732,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 613,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 181,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-90,61; 101,52</t>
+          <t>-82,48; 251,97</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-36,26%</t>
+          <t>-37,9%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,99</t>
+          <t>-3,96; 2,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,94; -0,16</t>
+          <t>-5,94; -0,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,93</t>
+          <t>-4,04; 0,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,56</t>
+          <t>-3,96; 1,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,28; 84,75</t>
+          <t>-66,78; 103,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,94; 9,1</t>
+          <t>-92,29; 19,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,12; 91,99</t>
+          <t>-89,25; 74,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,39; 178,94</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-40,57%</t>
+          <t>-31,01%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,84</t>
+          <t>-1,11; 1,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,64</t>
+          <t>-2,11; 0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,09</t>
+          <t>-1,66; 1,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,16</t>
+          <t>-2,63; 0,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,83; 88,36</t>
+          <t>-33,0; 81,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,97; 39,68</t>
+          <t>-61,45; 30,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 63,33</t>
+          <t>-50,94; 51,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-69,98; 8,57</t>
+          <t>-60,77; 28,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>77,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>130,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.7026459284774375</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.302493936830099</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.3275015465604811</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.1984402711620672</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.7793196639457286</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.309658071193105</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.1638379132680438</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1101476200447131</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,14; 3,78</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-0,77; 6,19</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,55; 3,84</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,16; 3,44</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-48,45; 1020,83</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-86,55; 558,61</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.138680120334721</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.7683988413375831</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.549232455317281</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.164910587257609</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-0.4844747805571414</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.8655319684159307</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.784568099431527</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.185200256675111</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.844291723225588</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.439532533963085</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>10.20831677821347</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>5.586071570075188</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-9,69%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-46,15%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>29,87%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-42,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,9; 2,12</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,58; 0,96</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,81; 3,82</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,13; 1,0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-67,65; 159,3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-85,85; 85,07</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-44,79; 202,36</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-81,34; 44,59</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.271613203650279</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.33011597602865</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9242565075141901</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.917666233798899</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.09694315730824947</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.4615348016341812</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.2986856144649461</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.423539597590448</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,17</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>137,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-23,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-58,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-17,62%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.900339657922654</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.576847654008186</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.808942430168742</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.127299485589386</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6764643432355042</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8585058863940256</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4478574113678025</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.8134449808734037</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,09; 6,17</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,56; 1,29</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,63; 0,84</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,66; 2,67</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-21,72; 732,56</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-82,48; 251,97</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.122683887525334</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9604574198134405</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.820239526074114</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.001131126627322</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.593035692489221</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.8507011431090085</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2.023602644949776</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.4459076699272077</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +811,289 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,67</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-22,93%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-65,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-50,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-37,9%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.665153217155575</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.3405918117602307</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.174779381874093</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.6094226502132437</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1.373322508739402</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.23104521738174</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.5810507313991191</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1761961800823104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,96; 2,4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,94; -0,09</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,04; 0,74</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,96; 1,45</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-66,78; 103,19</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-92,29; 19,88</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-89,25; 74,29</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-91,39; 178,94</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.08572966231487003</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.558160023766567</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.631577702390233</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.66267162966689</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2171686086687491</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="n">
+        <v>-0.8248009752484509</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.174920851012497</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.2924298600012</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8404198973593411</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.6663769282989</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>7.325553843349115</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="n">
+        <v>2.519733191126853</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.9983038834969913</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.674018640779973</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.460302993211738</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.061518780723265</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2292914757468467</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.6545751206416608</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.5023598825348717</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3790436386328552</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.956699756153479</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.936481702481561</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.040615111565222</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.959234257867468</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6678037861412732</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.9228601985485345</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.892509407635189</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.9138881107368373</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.395955043384611</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-0.0872850528092506</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.7431426642292359</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.451041752019721</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.031935182554317</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1987663528019686</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.7429025571739216</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.78937500144141</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-28,83%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-13,43%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-31,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,11; 1,71</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 0,57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,66; 1,03</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 0,61</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-33,0; 81,16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-61,45; 30,22</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-50,94; 51,19</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-60,77; 28,34</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.3479837377207973</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.7704541181367721</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.3472149470705965</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.043250879254245</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1304626181289897</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.2882546277689301</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1343284913305255</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.3101436614741644</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.112944902190396</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.105540800601796</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.659850253478587</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.63284861169541</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3299777658609955</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.6144771801611679</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.5094030581038214</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.6076596862543228</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.706172614419963</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5724335433685906</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.030436157666736</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.6145102464953157</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.8115986182338182</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3022012739288876</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.5118708275832577</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.2834139267962326</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1101,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
